--- a/pages/page3_dragon_cinema/content/dragon_scenes.xlsx
+++ b/pages/page3_dragon_cinema/content/dragon_scenes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Saurabh\Documents\AutoVideoAgent\pages\page3_dragon_cinema\content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4585D367-AD7F-470C-9B0A-B34D67B8DE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65450A76-6C89-4A17-ADAF-AE2DFED9180A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,9 +63,6 @@
     <t>A direct continuation in a frozen Arctic fjord at midnight, surrounded by knife-shaped glaciers, roaring blizzards, cracked black ice, and blue auroras flickering like war flames. Dragon description: a gigantic obsidian frost dragon built like an ancient apex predator, with armored black scales, jagged ice horns, torn battle-scarred wings, glowing cyan eyes, cracked teeth, and blue fire pulsing deep inside its throat. The same dragon continues fighting a rival glacier leviathan dragon exploding from below with frozen fangs, armored coils, and a tail powerful enough to split mountains. Continue the same battle with no reset as the rival dragon rises wounded and launches a furious counterattack, forcing both beasts into an even more violent close-range clash. Maintain exact continuity with Scene 1: same dragon design, same rival dragon, same battlefield damage, same weather, and same cinematic lighting. Make the action more dangerous and powerful with close-up jaws, claws, wing strikes, shockwaves, collapsing terrain, realistic creature movement, 9:16 vertical blockbuster VFX, 480p, 15-second scene, no cartoon style, no soft fantasy look.</t>
   </si>
   <si>
-    <t>10 sec</t>
-  </si>
-  <si>
     <t>480p</t>
   </si>
   <si>
@@ -991,13 +988,16 @@
   </si>
   <si>
     <t>#dragon #mountainheart #cosmic #fantasy</t>
+  </si>
+  <si>
+    <t>15 sec</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1010,6 +1010,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1421,22 +1427,22 @@
         <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="J2" s="2">
         <v>0</v>
@@ -1447,28 +1453,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="J3" s="2">
         <v>0</v>
@@ -1479,28 +1485,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J4" s="2">
         <v>0</v>
@@ -1511,28 +1517,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="J5" s="2">
         <v>0</v>
@@ -1543,28 +1549,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="J6" s="2">
         <v>0</v>
@@ -1575,28 +1581,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="J7" s="2">
         <v>0</v>
@@ -1607,28 +1613,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
@@ -1639,28 +1645,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="J9" s="2">
         <v>0</v>
@@ -1671,28 +1677,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="J10" s="2">
         <v>0</v>
@@ -1703,28 +1709,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="3" t="s">
+      <c r="I11" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="J11" s="2">
         <v>0</v>
@@ -1735,28 +1741,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="J12" s="2">
         <v>0</v>
@@ -1767,28 +1773,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="J13" s="2">
         <v>0</v>
@@ -1799,28 +1805,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="J14" s="2">
         <v>0</v>
@@ -1831,28 +1837,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="3" t="s">
+      <c r="I15" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="J15" s="2">
         <v>0</v>
@@ -1863,28 +1869,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="3" t="s">
+      <c r="I16" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="J16" s="2">
         <v>0</v>
@@ -1895,28 +1901,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="3" t="s">
+      <c r="I17" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="J17" s="2">
         <v>0</v>
@@ -1927,28 +1933,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="J18" s="2">
         <v>0</v>
@@ -1959,28 +1965,28 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="3" t="s">
+      <c r="I19" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="J19" s="2">
         <v>0</v>
@@ -1991,28 +1997,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="J20" s="2">
         <v>0</v>
@@ -2023,28 +2029,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="J21" s="2">
         <v>0</v>
@@ -2055,28 +2061,28 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="3" t="s">
+      <c r="I22" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="J22" s="2">
         <v>0</v>
@@ -2087,28 +2093,28 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="J23" s="2">
         <v>0</v>
@@ -2119,28 +2125,28 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="J24" s="2">
         <v>0</v>
@@ -2151,28 +2157,28 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="3" t="s">
+      <c r="I25" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="J25" s="2">
         <v>0</v>
@@ -2189,22 +2195,22 @@
         <v>11</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="J26" s="2">
         <v>0</v>
@@ -2215,28 +2221,28 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="J27" s="2">
         <v>0</v>
@@ -2247,28 +2253,28 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="J28" s="2">
         <v>0</v>
@@ -2279,28 +2285,28 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="D29" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H29" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="J29" s="2">
         <v>0</v>
@@ -2311,28 +2317,28 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="J30" s="2">
         <v>0</v>
@@ -2343,28 +2349,28 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="J31" s="2">
         <v>0</v>
@@ -2375,28 +2381,28 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="J32" s="2">
         <v>0</v>
@@ -2407,28 +2413,28 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="J33" s="2">
         <v>0</v>
@@ -2439,28 +2445,28 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D34" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H34" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="J34" s="2">
         <v>0</v>
@@ -2471,28 +2477,28 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H35" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="J35" s="2">
         <v>0</v>
@@ -2503,28 +2509,28 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="J36" s="2">
         <v>0</v>
@@ -2535,28 +2541,28 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H37" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="J37" s="2">
         <v>0</v>
@@ -2567,28 +2573,28 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H38" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="J38" s="2">
         <v>0</v>
@@ -2599,28 +2605,28 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H39" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="J39" s="2">
         <v>0</v>
@@ -2631,28 +2637,28 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H40" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="J40" s="2">
         <v>0</v>
@@ -2663,28 +2669,28 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H41" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="J41" s="2">
         <v>0</v>
@@ -2695,28 +2701,28 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="D42" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H42" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="J42" s="2">
         <v>0</v>
@@ -2727,28 +2733,28 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="D43" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H43" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="J43" s="2">
         <v>0</v>
@@ -2759,28 +2765,28 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H44" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="J44" s="2">
         <v>0</v>
@@ -2791,28 +2797,28 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D45" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H45" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="J45" s="2">
         <v>0</v>
@@ -2823,28 +2829,28 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="D46" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H46" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="J46" s="2">
         <v>0</v>
@@ -2855,28 +2861,28 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="D47" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H47" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="J47" s="2">
         <v>0</v>
@@ -2887,28 +2893,28 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="D48" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H48" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="J48" s="2">
         <v>0</v>
@@ -2919,28 +2925,28 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="D49" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H49" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="J49" s="2">
         <v>0</v>
@@ -2957,22 +2963,22 @@
         <v>11</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H50" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="J50" s="2">
         <v>0</v>
@@ -2983,28 +2989,28 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="D51" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H51" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="J51" s="2">
         <v>0</v>
@@ -3015,28 +3021,28 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="D52" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H52" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="J52" s="2">
         <v>0</v>
@@ -3047,28 +3053,28 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="D53" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="J53" s="2">
         <v>0</v>
@@ -3079,28 +3085,28 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D54" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H54" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="J54" s="2">
         <v>0</v>
@@ -3111,28 +3117,28 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="D55" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H55" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="J55" s="2">
         <v>0</v>
@@ -3143,28 +3149,28 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="D56" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H56" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I56" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="J56" s="2">
         <v>0</v>
@@ -3175,28 +3181,28 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D57" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H57" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I57" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="J57" s="2">
         <v>0</v>
@@ -3207,28 +3213,28 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D58" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H58" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="J58" s="2">
         <v>0</v>
@@ -3239,28 +3245,28 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D59" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H59" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="J59" s="2">
         <v>0</v>
@@ -3271,28 +3277,28 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="D60" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H60" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I60" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="J60" s="2">
         <v>0</v>
@@ -3303,28 +3309,28 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D61" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H61" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="J61" s="2">
         <v>0</v>
@@ -3335,28 +3341,28 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="D62" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H62" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="I62" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="J62" s="2">
         <v>0</v>
@@ -3367,28 +3373,28 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="D63" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H63" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I63" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="J63" s="2">
         <v>0</v>
@@ -3399,28 +3405,28 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="D64" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H64" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I64" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="J64" s="2">
         <v>0</v>
@@ -3431,28 +3437,28 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="D65" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H65" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I65" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="J65" s="2">
         <v>0</v>
@@ -3463,28 +3469,28 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="D66" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H66" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I66" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="J66" s="2">
         <v>0</v>
@@ -3495,28 +3501,28 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="D67" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H67" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I67" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="J67" s="2">
         <v>0</v>
@@ -3527,28 +3533,28 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="D68" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H68" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="I68" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="J68" s="2">
         <v>0</v>
@@ -3559,28 +3565,28 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D69" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H69" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I69" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="J69" s="2">
         <v>0</v>
@@ -3591,28 +3597,28 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="D70" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H70" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I70" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="J70" s="2">
         <v>0</v>
@@ -3623,28 +3629,28 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="D71" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H71" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I71" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>190</v>
       </c>
       <c r="J71" s="2">
         <v>0</v>
@@ -3655,28 +3661,28 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="D72" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H72" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="I72" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="J72" s="2">
         <v>0</v>
@@ -3687,28 +3693,28 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="D73" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H73" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I73" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="J73" s="2">
         <v>0</v>
@@ -3725,22 +3731,22 @@
         <v>11</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H74" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="I74" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="J74" s="2">
         <v>0</v>
@@ -3751,28 +3757,28 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="D75" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H75" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="I75" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="J75" s="2">
         <v>0</v>
@@ -3783,28 +3789,28 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C76" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="D76" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H76" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I76" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="J76" s="2">
         <v>0</v>
@@ -3815,28 +3821,28 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="D77" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H77" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I77" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="J77" s="2">
         <v>0</v>
@@ -3847,28 +3853,28 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D78" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H78" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I78" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>204</v>
       </c>
       <c r="J78" s="2">
         <v>0</v>
@@ -3879,28 +3885,28 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="D79" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H79" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="I79" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="J79" s="2">
         <v>0</v>
@@ -3911,28 +3917,28 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="D80" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H80" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="I80" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="J80" s="2">
         <v>0</v>
@@ -3943,28 +3949,28 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D81" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H81" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I81" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="J81" s="2">
         <v>0</v>
@@ -3975,28 +3981,28 @@
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D82" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H82" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I82" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="J82" s="2">
         <v>0</v>
@@ -4007,28 +4013,28 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C83" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D83" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H83" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="I83" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="J83" s="2">
         <v>0</v>
@@ -4039,28 +4045,28 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C84" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="D84" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H84" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="I84" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="J84" s="2">
         <v>0</v>
@@ -4071,28 +4077,28 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C85" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D85" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H85" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="I85" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="I85" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="J85" s="2">
         <v>0</v>
@@ -4103,28 +4109,28 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C86" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="D86" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H86" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="I86" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="J86" s="2">
         <v>0</v>
@@ -4135,28 +4141,28 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C87" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="D87" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H87" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="I87" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="J87" s="2">
         <v>0</v>
@@ -4167,28 +4173,28 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C88" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="D88" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H88" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I88" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="J88" s="2">
         <v>0</v>
@@ -4199,28 +4205,28 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="D89" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H89" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I89" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>226</v>
       </c>
       <c r="J89" s="2">
         <v>0</v>
@@ -4231,28 +4237,28 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C90" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="D90" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H90" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I90" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="I90" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="J90" s="2">
         <v>0</v>
@@ -4263,28 +4269,28 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C91" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="D91" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H91" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="I91" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="J91" s="2">
         <v>0</v>
@@ -4295,28 +4301,28 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="D92" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H92" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="I92" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="J92" s="2">
         <v>0</v>
@@ -4327,28 +4333,28 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C93" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D93" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H93" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="I93" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="J93" s="2">
         <v>0</v>
@@ -4359,28 +4365,28 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="D94" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H94" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="I94" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="J94" s="2">
         <v>0</v>
@@ -4391,28 +4397,28 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C95" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="D95" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H95" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="I95" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="J95" s="2">
         <v>0</v>
@@ -4423,28 +4429,28 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C96" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="D96" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H96" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="I96" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="J96" s="2">
         <v>0</v>
@@ -4455,28 +4461,28 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C97" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="D97" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H97" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="I97" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="J97" s="2">
         <v>0</v>
@@ -4493,22 +4499,22 @@
         <v>11</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H98" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="I98" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>244</v>
       </c>
       <c r="J98" s="2">
         <v>0</v>
@@ -4519,28 +4525,28 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C99" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="D99" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H99" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I99" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="J99" s="2">
         <v>0</v>
@@ -4551,28 +4557,28 @@
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C100" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="D100" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H100" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I100" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="J100" s="2">
         <v>0</v>
@@ -4583,28 +4589,28 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C101" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="D101" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H101" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="I101" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="J101" s="2">
         <v>0</v>
@@ -4615,28 +4621,28 @@
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C102" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D102" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H102" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="I102" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="J102" s="2">
         <v>0</v>
@@ -4647,28 +4653,28 @@
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C103" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="D103" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H103" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I103" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="I103" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="J103" s="2">
         <v>0</v>
@@ -4679,28 +4685,28 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C104" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="D104" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H104" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I104" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>226</v>
       </c>
       <c r="J104" s="2">
         <v>0</v>
@@ -4711,28 +4717,28 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C105" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D105" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H105" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I105" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="J105" s="2">
         <v>0</v>
@@ -4743,28 +4749,28 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C106" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D106" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H106" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="I106" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="I106" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="J106" s="2">
         <v>0</v>
@@ -4775,28 +4781,28 @@
         <v>156</v>
       </c>
       <c r="B107" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C107" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D107" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H107" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="I107" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="I107" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="J107" s="2">
         <v>0</v>
@@ -4807,28 +4813,28 @@
         <v>157</v>
       </c>
       <c r="B108" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C108" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C108" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="D108" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H108" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="I108" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="I108" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="J108" s="2">
         <v>0</v>
@@ -4839,28 +4845,28 @@
         <v>158</v>
       </c>
       <c r="B109" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C109" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D109" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H109" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I109" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="I109" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="J109" s="2">
         <v>0</v>
@@ -4871,28 +4877,28 @@
         <v>159</v>
       </c>
       <c r="B110" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C110" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="D110" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H110" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="I110" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="I110" s="3" t="s">
-        <v>258</v>
       </c>
       <c r="J110" s="2">
         <v>0</v>
@@ -4903,28 +4909,28 @@
         <v>160</v>
       </c>
       <c r="B111" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C111" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="D111" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H111" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="I111" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="I111" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="J111" s="2">
         <v>0</v>
@@ -4935,28 +4941,28 @@
         <v>161</v>
       </c>
       <c r="B112" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C112" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="D112" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H112" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="I112" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="I112" s="3" t="s">
-        <v>262</v>
       </c>
       <c r="J112" s="2">
         <v>0</v>
@@ -4967,28 +4973,28 @@
         <v>162</v>
       </c>
       <c r="B113" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C113" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="D113" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H113" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="I113" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="I113" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="J113" s="2">
         <v>0</v>
@@ -4999,28 +5005,28 @@
         <v>163</v>
       </c>
       <c r="B114" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C114" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C114" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="D114" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H114" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="I114" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="I114" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="J114" s="2">
         <v>0</v>
@@ -5031,28 +5037,28 @@
         <v>164</v>
       </c>
       <c r="B115" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C115" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="D115" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H115" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="I115" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="I115" s="3" t="s">
-        <v>268</v>
       </c>
       <c r="J115" s="2">
         <v>0</v>
@@ -5063,28 +5069,28 @@
         <v>165</v>
       </c>
       <c r="B116" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C116" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="D116" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H116" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="I116" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="I116" s="3" t="s">
-        <v>270</v>
       </c>
       <c r="J116" s="2">
         <v>0</v>
@@ -5095,28 +5101,28 @@
         <v>166</v>
       </c>
       <c r="B117" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C117" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D117" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H117" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="I117" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="I117" s="3" t="s">
-        <v>272</v>
       </c>
       <c r="J117" s="2">
         <v>0</v>
@@ -5127,28 +5133,28 @@
         <v>167</v>
       </c>
       <c r="B118" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C118" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C118" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="D118" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H118" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="I118" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="I118" s="3" t="s">
-        <v>274</v>
       </c>
       <c r="J118" s="2">
         <v>0</v>
@@ -5159,28 +5165,28 @@
         <v>168</v>
       </c>
       <c r="B119" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C119" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="D119" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H119" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="I119" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="I119" s="3" t="s">
-        <v>276</v>
       </c>
       <c r="J119" s="2">
         <v>0</v>
@@ -5191,28 +5197,28 @@
         <v>169</v>
       </c>
       <c r="B120" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C120" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C120" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="D120" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H120" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I120" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="I120" s="3" t="s">
-        <v>278</v>
       </c>
       <c r="J120" s="2">
         <v>0</v>
@@ -5223,28 +5229,28 @@
         <v>170</v>
       </c>
       <c r="B121" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C121" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="D121" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H121" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="I121" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="I121" s="3" t="s">
-        <v>280</v>
       </c>
       <c r="J121" s="2">
         <v>0</v>
@@ -5261,22 +5267,22 @@
         <v>11</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J122" s="2">
         <v>0</v>
@@ -5287,28 +5293,28 @@
         <v>172</v>
       </c>
       <c r="B123" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C123" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="D123" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J123" s="2">
         <v>0</v>
@@ -5319,28 +5325,28 @@
         <v>173</v>
       </c>
       <c r="B124" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C124" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="D124" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J124" s="2">
         <v>0</v>
@@ -5351,28 +5357,28 @@
         <v>174</v>
       </c>
       <c r="B125" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C125" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="D125" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H125" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="I125" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="I125" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="J125" s="2">
         <v>0</v>
@@ -5383,28 +5389,28 @@
         <v>175</v>
       </c>
       <c r="B126" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C126" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D126" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J126" s="2">
         <v>0</v>
@@ -5415,28 +5421,28 @@
         <v>176</v>
       </c>
       <c r="B127" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C127" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="D127" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H127" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I127" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="I127" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="J127" s="2">
         <v>0</v>
@@ -5447,28 +5453,28 @@
         <v>177</v>
       </c>
       <c r="B128" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C128" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="D128" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J128" s="2">
         <v>0</v>
@@ -5479,28 +5485,28 @@
         <v>178</v>
       </c>
       <c r="B129" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C129" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D129" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J129" s="2">
         <v>0</v>
@@ -5511,28 +5517,28 @@
         <v>179</v>
       </c>
       <c r="B130" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C130" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C130" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D130" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J130" s="2">
         <v>0</v>
@@ -5543,28 +5549,28 @@
         <v>180</v>
       </c>
       <c r="B131" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C131" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C131" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D131" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H131" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="I131" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="I131" s="3" t="s">
-        <v>293</v>
       </c>
       <c r="J131" s="2">
         <v>0</v>
@@ -5575,28 +5581,28 @@
         <v>181</v>
       </c>
       <c r="B132" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C132" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C132" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="D132" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J132" s="2">
         <v>0</v>
@@ -5607,28 +5613,28 @@
         <v>182</v>
       </c>
       <c r="B133" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C133" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C133" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D133" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J133" s="2">
         <v>0</v>
@@ -5639,28 +5645,28 @@
         <v>183</v>
       </c>
       <c r="B134" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C134" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C134" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="D134" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J134" s="2">
         <v>0</v>
@@ -5671,28 +5677,28 @@
         <v>184</v>
       </c>
       <c r="B135" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C135" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C135" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="D135" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J135" s="2">
         <v>0</v>
@@ -5703,28 +5709,28 @@
         <v>185</v>
       </c>
       <c r="B136" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C136" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C136" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="D136" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J136" s="2">
         <v>0</v>
@@ -5735,28 +5741,28 @@
         <v>186</v>
       </c>
       <c r="B137" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C137" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C137" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="D137" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J137" s="2">
         <v>0</v>
@@ -5767,28 +5773,28 @@
         <v>187</v>
       </c>
       <c r="B138" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C138" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C138" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="D138" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J138" s="2">
         <v>0</v>
@@ -5799,28 +5805,28 @@
         <v>188</v>
       </c>
       <c r="B139" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C139" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C139" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="D139" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H139" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="I139" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="I139" s="3" t="s">
-        <v>302</v>
       </c>
       <c r="J139" s="2">
         <v>0</v>
@@ -5831,28 +5837,28 @@
         <v>189</v>
       </c>
       <c r="B140" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C140" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="D140" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J140" s="2">
         <v>0</v>
@@ -5863,28 +5869,28 @@
         <v>190</v>
       </c>
       <c r="B141" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C141" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C141" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D141" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J141" s="2">
         <v>0</v>
@@ -5895,28 +5901,28 @@
         <v>191</v>
       </c>
       <c r="B142" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C142" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C142" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="D142" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J142" s="2">
         <v>0</v>
@@ -5927,28 +5933,28 @@
         <v>192</v>
       </c>
       <c r="B143" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C143" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C143" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="D143" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H143" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="I143" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="I143" s="3" t="s">
-        <v>307</v>
       </c>
       <c r="J143" s="2">
         <v>0</v>
@@ -5959,28 +5965,28 @@
         <v>193</v>
       </c>
       <c r="B144" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C144" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C144" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="D144" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J144" s="2">
         <v>0</v>
@@ -5991,28 +5997,28 @@
         <v>194</v>
       </c>
       <c r="B145" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C145" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C145" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="D145" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J145" s="2">
         <v>0</v>
@@ -6029,22 +6035,22 @@
         <v>11</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I146" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J146" s="2">
         <v>0</v>
@@ -6055,28 +6061,28 @@
         <v>196</v>
       </c>
       <c r="B147" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C147" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="D147" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J147" s="2">
         <v>0</v>
@@ -6087,28 +6093,28 @@
         <v>197</v>
       </c>
       <c r="B148" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C148" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C148" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="D148" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J148" s="2">
         <v>0</v>
@@ -6119,28 +6125,28 @@
         <v>198</v>
       </c>
       <c r="B149" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C149" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C149" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="D149" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I149" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J149" s="2">
         <v>0</v>
@@ -6151,28 +6157,28 @@
         <v>199</v>
       </c>
       <c r="B150" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C150" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C150" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D150" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J150" s="2">
         <v>0</v>
@@ -6183,28 +6189,28 @@
         <v>200</v>
       </c>
       <c r="B151" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C151" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C151" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="D151" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I151" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J151" s="2">
         <v>0</v>
@@ -6215,28 +6221,28 @@
         <v>201</v>
       </c>
       <c r="B152" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C152" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C152" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="D152" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H152" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="I152" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="I152" s="3" t="s">
-        <v>317</v>
       </c>
       <c r="J152" s="2">
         <v>0</v>
@@ -6247,28 +6253,28 @@
         <v>202</v>
       </c>
       <c r="B153" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C153" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C153" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D153" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I153" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J153" s="2">
         <v>0</v>
@@ -6279,28 +6285,28 @@
         <v>203</v>
       </c>
       <c r="B154" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C154" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C154" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D154" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I154" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J154" s="2">
         <v>0</v>
@@ -6311,28 +6317,28 @@
         <v>204</v>
       </c>
       <c r="B155" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C155" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C155" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D155" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I155" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J155" s="2">
         <v>0</v>
@@ -6343,28 +6349,28 @@
         <v>205</v>
       </c>
       <c r="B156" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C156" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C156" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="D156" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J156" s="2">
         <v>0</v>
@@ -6375,28 +6381,28 @@
         <v>206</v>
       </c>
       <c r="B157" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C157" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C157" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D157" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H157" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="I157" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="I157" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="J157" s="2">
         <v>0</v>
@@ -6407,28 +6413,28 @@
         <v>207</v>
       </c>
       <c r="B158" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C158" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C158" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="D158" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H158" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="I158" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="I158" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="J158" s="2">
         <v>0</v>
@@ -6439,28 +6445,28 @@
         <v>208</v>
       </c>
       <c r="B159" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C159" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C159" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="D159" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H159" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I159" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="I159" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="J159" s="2">
         <v>0</v>
@@ -6471,28 +6477,28 @@
         <v>209</v>
       </c>
       <c r="B160" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C160" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C160" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="D160" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H160" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="I160" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="I160" s="3" t="s">
-        <v>258</v>
       </c>
       <c r="J160" s="2">
         <v>0</v>
@@ -6503,28 +6509,28 @@
         <v>210</v>
       </c>
       <c r="B161" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C161" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C161" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="D161" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H161" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="I161" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="I161" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="J161" s="2">
         <v>0</v>
@@ -6535,28 +6541,28 @@
         <v>211</v>
       </c>
       <c r="B162" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C162" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C162" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="D162" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H162" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="I162" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="I162" s="3" t="s">
-        <v>262</v>
       </c>
       <c r="J162" s="2">
         <v>0</v>
@@ -6567,28 +6573,28 @@
         <v>212</v>
       </c>
       <c r="B163" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C163" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C163" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="D163" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H163" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="I163" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="I163" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="J163" s="2">
         <v>0</v>
@@ -6599,28 +6605,28 @@
         <v>213</v>
       </c>
       <c r="B164" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C164" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C164" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="D164" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H164" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="I164" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="I164" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="J164" s="2">
         <v>0</v>
@@ -6631,28 +6637,28 @@
         <v>214</v>
       </c>
       <c r="B165" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C165" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C165" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D165" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H165" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="I165" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="I165" s="3" t="s">
-        <v>268</v>
       </c>
       <c r="J165" s="2">
         <v>0</v>
@@ -6663,28 +6669,28 @@
         <v>215</v>
       </c>
       <c r="B166" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C166" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C166" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="D166" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H166" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="I166" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="I166" s="3" t="s">
-        <v>270</v>
       </c>
       <c r="J166" s="2">
         <v>0</v>
@@ -6695,28 +6701,28 @@
         <v>216</v>
       </c>
       <c r="B167" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C167" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C167" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="D167" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H167" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="I167" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="I167" s="3" t="s">
-        <v>272</v>
       </c>
       <c r="J167" s="2">
         <v>0</v>
@@ -6727,28 +6733,28 @@
         <v>217</v>
       </c>
       <c r="B168" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C168" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C168" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="D168" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H168" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="I168" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="I168" s="3" t="s">
-        <v>274</v>
       </c>
       <c r="J168" s="2">
         <v>0</v>
@@ -6759,28 +6765,28 @@
         <v>218</v>
       </c>
       <c r="B169" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C169" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C169" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="D169" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H169" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="I169" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="I169" s="3" t="s">
-        <v>276</v>
       </c>
       <c r="J169" s="2">
         <v>0</v>
@@ -6797,22 +6803,22 @@
         <v>11</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H170" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I170" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="I170" s="3" t="s">
-        <v>278</v>
       </c>
       <c r="J170" s="2">
         <v>0</v>
@@ -6823,28 +6829,28 @@
         <v>220</v>
       </c>
       <c r="B171" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C171" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="D171" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H171" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="I171" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="I171" s="3" t="s">
-        <v>280</v>
       </c>
       <c r="J171" s="2">
         <v>0</v>
@@ -6855,28 +6861,28 @@
         <v>221</v>
       </c>
       <c r="B172" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C172" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C172" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="D172" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J172" s="2">
         <v>0</v>
@@ -6887,28 +6893,28 @@
         <v>222</v>
       </c>
       <c r="B173" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C173" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C173" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="D173" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H173" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I173" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J173" s="2">
         <v>0</v>
@@ -6919,28 +6925,28 @@
         <v>223</v>
       </c>
       <c r="B174" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C174" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C174" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D174" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I174" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J174" s="2">
         <v>0</v>
@@ -6951,28 +6957,28 @@
         <v>224</v>
       </c>
       <c r="B175" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C175" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C175" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="D175" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H175" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="I175" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="I175" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="J175" s="2">
         <v>0</v>
@@ -6983,28 +6989,28 @@
         <v>225</v>
       </c>
       <c r="B176" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C176" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C176" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="D176" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J176" s="2">
         <v>0</v>
@@ -7015,28 +7021,28 @@
         <v>226</v>
       </c>
       <c r="B177" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C177" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C177" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D177" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H177" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I177" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="I177" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="J177" s="2">
         <v>0</v>
@@ -7047,28 +7053,28 @@
         <v>227</v>
       </c>
       <c r="B178" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C178" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C178" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D178" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J178" s="2">
         <v>0</v>
@@ -7079,28 +7085,28 @@
         <v>228</v>
       </c>
       <c r="B179" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C179" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C179" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D179" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I179" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J179" s="2">
         <v>0</v>
@@ -7111,28 +7117,28 @@
         <v>229</v>
       </c>
       <c r="B180" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C180" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C180" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="D180" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I180" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J180" s="2">
         <v>0</v>
@@ -7143,28 +7149,28 @@
         <v>230</v>
       </c>
       <c r="B181" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C181" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C181" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D181" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H181" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="I181" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="I181" s="3" t="s">
-        <v>293</v>
       </c>
       <c r="J181" s="2">
         <v>0</v>
@@ -7175,28 +7181,28 @@
         <v>231</v>
       </c>
       <c r="B182" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C182" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C182" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="D182" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J182" s="2">
         <v>0</v>
@@ -7207,28 +7213,28 @@
         <v>232</v>
       </c>
       <c r="B183" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C183" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C183" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="D183" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I183" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J183" s="2">
         <v>0</v>
@@ -7239,28 +7245,28 @@
         <v>233</v>
       </c>
       <c r="B184" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C184" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C184" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="D184" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J184" s="2">
         <v>0</v>
@@ -7271,28 +7277,28 @@
         <v>234</v>
       </c>
       <c r="B185" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C185" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C185" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="D185" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I185" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J185" s="2">
         <v>0</v>
@@ -7303,28 +7309,28 @@
         <v>235</v>
       </c>
       <c r="B186" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C186" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C186" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="D186" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I186" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J186" s="2">
         <v>0</v>
@@ -7335,28 +7341,28 @@
         <v>236</v>
       </c>
       <c r="B187" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C187" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C187" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="D187" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I187" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J187" s="2">
         <v>0</v>
@@ -7367,28 +7373,28 @@
         <v>237</v>
       </c>
       <c r="B188" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C188" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C188" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="D188" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I188" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J188" s="2">
         <v>0</v>
@@ -7399,28 +7405,28 @@
         <v>238</v>
       </c>
       <c r="B189" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C189" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C189" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D189" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H189" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="I189" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="I189" s="3" t="s">
-        <v>302</v>
       </c>
       <c r="J189" s="2">
         <v>0</v>
@@ -7431,28 +7437,28 @@
         <v>239</v>
       </c>
       <c r="B190" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C190" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C190" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="D190" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I190" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J190" s="2">
         <v>0</v>
@@ -7463,28 +7469,28 @@
         <v>240</v>
       </c>
       <c r="B191" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C191" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C191" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="D191" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H191" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I191" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J191" s="2">
         <v>0</v>
@@ -7495,28 +7501,28 @@
         <v>241</v>
       </c>
       <c r="B192" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C192" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C192" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="D192" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I192" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J192" s="2">
         <v>0</v>
@@ -7527,28 +7533,28 @@
         <v>242</v>
       </c>
       <c r="B193" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C193" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C193" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="D193" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H193" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="I193" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="I193" s="3" t="s">
-        <v>307</v>
       </c>
       <c r="J193" s="2">
         <v>0</v>
@@ -7565,22 +7571,22 @@
         <v>11</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H194" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I194" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J194" s="2">
         <v>0</v>
@@ -7591,28 +7597,28 @@
         <v>244</v>
       </c>
       <c r="B195" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C195" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="D195" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H195" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I195" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J195" s="2">
         <v>0</v>
@@ -7623,28 +7629,28 @@
         <v>245</v>
       </c>
       <c r="B196" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C196" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C196" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="D196" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H196" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I196" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J196" s="2">
         <v>0</v>
@@ -7655,28 +7661,28 @@
         <v>246</v>
       </c>
       <c r="B197" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C197" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C197" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="D197" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I197" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J197" s="2">
         <v>0</v>
@@ -7687,28 +7693,28 @@
         <v>247</v>
       </c>
       <c r="B198" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C198" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C198" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D198" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I198" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J198" s="2">
         <v>0</v>
@@ -7719,28 +7725,28 @@
         <v>248</v>
       </c>
       <c r="B199" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C199" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C199" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="D199" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I199" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J199" s="2">
         <v>0</v>
@@ -7751,28 +7757,28 @@
         <v>249</v>
       </c>
       <c r="B200" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C200" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C200" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="D200" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H200" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I200" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J200" s="2">
         <v>0</v>
@@ -7783,28 +7789,28 @@
         <v>250</v>
       </c>
       <c r="B201" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C201" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C201" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D201" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I201" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J201" s="2">
         <v>0</v>
@@ -7815,28 +7821,28 @@
         <v>251</v>
       </c>
       <c r="B202" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C202" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C202" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D202" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H202" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="I202" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="I202" s="3" t="s">
-        <v>317</v>
       </c>
       <c r="J202" s="2">
         <v>0</v>
@@ -7847,28 +7853,28 @@
         <v>252</v>
       </c>
       <c r="B203" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C203" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C203" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D203" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I203" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J203" s="2">
         <v>0</v>
@@ -7879,28 +7885,28 @@
         <v>253</v>
       </c>
       <c r="B204" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C204" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C204" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="D204" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I204" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J204" s="2">
         <v>0</v>
@@ -7911,28 +7917,28 @@
         <v>254</v>
       </c>
       <c r="B205" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C205" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C205" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D205" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I205" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J205" s="2">
         <v>0</v>
@@ -7943,28 +7949,28 @@
         <v>255</v>
       </c>
       <c r="B206" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C206" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C206" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="D206" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I206" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J206" s="2">
         <v>0</v>
@@ -7975,28 +7981,28 @@
         <v>256</v>
       </c>
       <c r="B207" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C207" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C207" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="D207" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H207" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="I207" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="I207" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="J207" s="2">
         <v>0</v>
@@ -8007,28 +8013,28 @@
         <v>257</v>
       </c>
       <c r="B208" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C208" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C208" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="D208" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H208" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="I208" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="I208" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="J208" s="2">
         <v>0</v>
@@ -8039,28 +8045,28 @@
         <v>258</v>
       </c>
       <c r="B209" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C209" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C209" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="D209" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H209" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I209" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="I209" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="J209" s="2">
         <v>0</v>
@@ -8071,28 +8077,28 @@
         <v>259</v>
       </c>
       <c r="B210" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C210" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C210" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="D210" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H210" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="I210" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="I210" s="3" t="s">
-        <v>258</v>
       </c>
       <c r="J210" s="2">
         <v>0</v>
@@ -8103,28 +8109,28 @@
         <v>260</v>
       </c>
       <c r="B211" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C211" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C211" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="D211" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H211" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="I211" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="I211" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="J211" s="2">
         <v>0</v>
@@ -8135,28 +8141,28 @@
         <v>261</v>
       </c>
       <c r="B212" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C212" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C212" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="D212" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H212" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="I212" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="I212" s="3" t="s">
-        <v>262</v>
       </c>
       <c r="J212" s="2">
         <v>0</v>
@@ -8167,28 +8173,28 @@
         <v>262</v>
       </c>
       <c r="B213" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C213" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C213" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D213" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H213" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="I213" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="I213" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="J213" s="2">
         <v>0</v>
@@ -8199,28 +8205,28 @@
         <v>263</v>
       </c>
       <c r="B214" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C214" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C214" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="D214" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H214" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="I214" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="I214" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="J214" s="2">
         <v>0</v>
@@ -8231,28 +8237,28 @@
         <v>264</v>
       </c>
       <c r="B215" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C215" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C215" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="D215" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H215" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="I215" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="I215" s="3" t="s">
-        <v>268</v>
       </c>
       <c r="J215" s="2">
         <v>0</v>
@@ -8263,28 +8269,28 @@
         <v>265</v>
       </c>
       <c r="B216" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C216" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C216" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="D216" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H216" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="I216" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="I216" s="3" t="s">
-        <v>270</v>
       </c>
       <c r="J216" s="2">
         <v>0</v>
@@ -8295,28 +8301,28 @@
         <v>266</v>
       </c>
       <c r="B217" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C217" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C217" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="D217" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H217" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="I217" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="I217" s="3" t="s">
-        <v>272</v>
       </c>
       <c r="J217" s="2">
         <v>0</v>
@@ -8333,22 +8339,22 @@
         <v>11</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H218" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="I218" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="I218" s="3" t="s">
-        <v>274</v>
       </c>
       <c r="J218" s="2">
         <v>0</v>
@@ -8359,28 +8365,28 @@
         <v>268</v>
       </c>
       <c r="B219" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C219" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C219" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="D219" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H219" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="I219" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="I219" s="3" t="s">
-        <v>276</v>
       </c>
       <c r="J219" s="2">
         <v>0</v>
@@ -8391,28 +8397,28 @@
         <v>269</v>
       </c>
       <c r="B220" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C220" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C220" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="D220" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H220" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I220" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="I220" s="3" t="s">
-        <v>278</v>
       </c>
       <c r="J220" s="2">
         <v>0</v>
@@ -8423,28 +8429,28 @@
         <v>270</v>
       </c>
       <c r="B221" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C221" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C221" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="D221" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H221" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="I221" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="I221" s="3" t="s">
-        <v>280</v>
       </c>
       <c r="J221" s="2">
         <v>0</v>
@@ -8455,28 +8461,28 @@
         <v>271</v>
       </c>
       <c r="B222" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C222" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C222" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D222" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H222" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I222" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J222" s="2">
         <v>0</v>
@@ -8487,28 +8493,28 @@
         <v>272</v>
       </c>
       <c r="B223" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C223" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C223" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="D223" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H223" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I223" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J223" s="2">
         <v>0</v>
@@ -8519,28 +8525,28 @@
         <v>273</v>
       </c>
       <c r="B224" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C224" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C224" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="D224" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H224" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I224" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J224" s="2">
         <v>0</v>
@@ -8551,28 +8557,28 @@
         <v>274</v>
       </c>
       <c r="B225" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C225" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C225" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D225" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H225" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="I225" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="I225" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="J225" s="2">
         <v>0</v>
@@ -8583,28 +8589,28 @@
         <v>275</v>
       </c>
       <c r="B226" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C226" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C226" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D226" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H226" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I226" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J226" s="2">
         <v>0</v>
@@ -8615,28 +8621,28 @@
         <v>276</v>
       </c>
       <c r="B227" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C227" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C227" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D227" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H227" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I227" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="I227" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="J227" s="2">
         <v>0</v>
@@ -8647,28 +8653,28 @@
         <v>277</v>
       </c>
       <c r="B228" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C228" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C228" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="D228" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I228" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J228" s="2">
         <v>0</v>
@@ -8679,28 +8685,28 @@
         <v>278</v>
       </c>
       <c r="B229" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C229" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C229" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D229" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I229" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J229" s="2">
         <v>0</v>
@@ -8711,28 +8717,28 @@
         <v>279</v>
       </c>
       <c r="B230" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C230" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C230" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="D230" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H230" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I230" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J230" s="2">
         <v>0</v>
@@ -8743,28 +8749,28 @@
         <v>280</v>
       </c>
       <c r="B231" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C231" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C231" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="D231" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H231" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="I231" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="I231" s="3" t="s">
-        <v>293</v>
       </c>
       <c r="J231" s="2">
         <v>0</v>
@@ -8775,28 +8781,28 @@
         <v>281</v>
       </c>
       <c r="B232" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C232" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C232" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="D232" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H232" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I232" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J232" s="2">
         <v>0</v>
@@ -8807,28 +8813,28 @@
         <v>282</v>
       </c>
       <c r="B233" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C233" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C233" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="D233" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H233" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I233" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J233" s="2">
         <v>0</v>
@@ -8839,28 +8845,28 @@
         <v>283</v>
       </c>
       <c r="B234" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C234" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C234" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="D234" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I234" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J234" s="2">
         <v>0</v>
@@ -8871,28 +8877,28 @@
         <v>284</v>
       </c>
       <c r="B235" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C235" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C235" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="D235" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H235" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I235" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J235" s="2">
         <v>0</v>
@@ -8903,28 +8909,28 @@
         <v>285</v>
       </c>
       <c r="B236" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C236" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C236" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="D236" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H236" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I236" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J236" s="2">
         <v>0</v>
@@ -8935,28 +8941,28 @@
         <v>286</v>
       </c>
       <c r="B237" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C237" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C237" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D237" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H237" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I237" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J237" s="2">
         <v>0</v>
@@ -8967,28 +8973,28 @@
         <v>287</v>
       </c>
       <c r="B238" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C238" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C238" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="D238" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H238" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I238" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J238" s="2">
         <v>0</v>
@@ -8999,28 +9005,28 @@
         <v>288</v>
       </c>
       <c r="B239" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C239" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C239" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="D239" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H239" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="I239" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="I239" s="3" t="s">
-        <v>302</v>
       </c>
       <c r="J239" s="2">
         <v>0</v>
@@ -9031,28 +9037,28 @@
         <v>289</v>
       </c>
       <c r="B240" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C240" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C240" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="D240" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H240" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I240" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J240" s="2">
         <v>0</v>
@@ -9063,28 +9069,28 @@
         <v>290</v>
       </c>
       <c r="B241" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C241" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C241" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="D241" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H241" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I241" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J241" s="2">
         <v>0</v>
@@ -9101,22 +9107,22 @@
         <v>11</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H242" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I242" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J242" s="2">
         <v>0</v>
@@ -9127,28 +9133,28 @@
         <v>292</v>
       </c>
       <c r="B243" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C243" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C243" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="D243" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H243" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="I243" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="I243" s="3" t="s">
-        <v>307</v>
       </c>
       <c r="J243" s="2">
         <v>0</v>
@@ -9159,28 +9165,28 @@
         <v>293</v>
       </c>
       <c r="B244" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C244" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C244" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="D244" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H244" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I244" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J244" s="2">
         <v>0</v>
@@ -9191,28 +9197,28 @@
         <v>294</v>
       </c>
       <c r="B245" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C245" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C245" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="D245" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H245" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I245" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J245" s="2">
         <v>0</v>
@@ -9223,28 +9229,28 @@
         <v>295</v>
       </c>
       <c r="B246" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C246" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C246" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D246" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H246" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I246" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J246" s="2">
         <v>0</v>
@@ -9255,28 +9261,28 @@
         <v>296</v>
       </c>
       <c r="B247" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C247" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C247" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="D247" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I247" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J247" s="2">
         <v>0</v>
@@ -9287,28 +9293,28 @@
         <v>297</v>
       </c>
       <c r="B248" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C248" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C248" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="D248" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H248" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I248" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J248" s="2">
         <v>0</v>
@@ -9319,28 +9325,28 @@
         <v>298</v>
       </c>
       <c r="B249" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C249" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C249" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D249" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H249" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I249" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J249" s="2">
         <v>0</v>
@@ -9351,28 +9357,28 @@
         <v>299</v>
       </c>
       <c r="B250" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C250" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C250" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D250" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I250" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J250" s="2">
         <v>0</v>
@@ -9383,28 +9389,28 @@
         <v>300</v>
       </c>
       <c r="B251" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C251" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C251" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D251" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H251" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I251" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J251" s="2">
         <v>0</v>
@@ -9415,28 +9421,28 @@
         <v>301</v>
       </c>
       <c r="B252" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C252" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C252" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="D252" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H252" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="I252" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="I252" s="3" t="s">
-        <v>317</v>
       </c>
       <c r="J252" s="2">
         <v>0</v>
@@ -9447,28 +9453,28 @@
         <v>302</v>
       </c>
       <c r="B253" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C253" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C253" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D253" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H253" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I253" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J253" s="2">
         <v>0</v>
@@ -9479,28 +9485,28 @@
         <v>303</v>
       </c>
       <c r="B254" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C254" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C254" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="D254" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H254" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I254" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J254" s="2">
         <v>0</v>
@@ -9511,28 +9517,28 @@
         <v>304</v>
       </c>
       <c r="B255" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C255" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C255" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="D255" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H255" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I255" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J255" s="2">
         <v>0</v>
@@ -9543,34 +9549,35 @@
         <v>305</v>
       </c>
       <c r="B256" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C256" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C256" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="D256" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H256" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I256" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J256" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>